--- a/experiment_results/wedos_grid/rtt_bursts_S2_atk1pct_wu450000_stage1b_rep3.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S2_atk1pct_wu450000_stage1b_rep3.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
